--- a/themes/loyaltyProgram.xlsx
+++ b/themes/loyaltyProgram.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -450,27 +450,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">        2. Внизу страницы [«Сервисы»]({{$temp.bonusLink}})</t>
+          <t xml:space="preserve">        2. Далее «Управление» –&gt; [«Уралсиб Бонус»]({{$temp.bonusLink}})</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">        2. Внизу страницы [«Сервисы»]({{$temp.bonusLink}}).</t>
+          <t xml:space="preserve">        2. Далее «Управление» -&gt; [«Уралсиб Бонус»]({{$temp.bonusLink}})</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>добавлена точка — для единообразия с первым пунктом списка (стр. 38), где точка есть</t>
+          <t>эн-дефис в стрелке-разделителе заменён на дефис (для единообразия с «-&gt;» в остальном файле)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -479,62 +479,62 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">        2. Далее «Управление» -&gt; [«Уралсиб Бонус»]({{$temp.bonusLink}}).</t>
+          <t xml:space="preserve">        2. Далее «Управление» -&gt; [«Уралсиб Бонус»]({{$temp.bonusLink}})</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>эн-дефис в стрелке-разделителе заменён на дефис (для единообразия с «-&gt;» в остальном файле); добавлена точка в конце предложения</t>
+          <t>эн-дефис в стрелке-разделителе заменён на дефис</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">        2. Внизу страницы [«Сервисы»]({{$temp.bonusLink}})</t>
+          <t xml:space="preserve">        3. Операции, подходящие по критериям (дата и сумма) будут маркированы зеленой иконкой.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">        2. Внизу страницы [«Сервисы»]({{$temp.bonusLink}}).</t>
+          <t xml:space="preserve">        2. Операции, подходящие по критериям (дата и сумма), будут маркированы зеленой иконкой.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>добавлена точка — для единообразия с первым пунктом списка (стр. 55), где точка есть</t>
+          <t>исправлена нумерация шага «3.» → «2.» (после шага 1 сразу шёл шаг 3, ср. с блоком Authorized ниже); добавлена запятая, закрывающая уточнение «(дата и сумма)»</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        2. Далее «Управление» –&gt; [«Уралсиб Бонус»]({{$temp.bonusLink}})</t>
+          <t xml:space="preserve">        4. Выберите подходящую покупку и нажмите «Компенсировать».</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">        2. Далее «Управление» -&gt; [«Уралсиб Бонус»]({{$temp.bonusLink}}).</t>
+          <t xml:space="preserve">        3. Выберите подходящую покупку и нажмите «Компенсировать».</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>эн-дефис в стрелке-разделителе заменён на дефис; добавлена точка в конце предложения</t>
+          <t>исправлена нумерация шага «4.» → «3.» вслед за исправлением предыдущего шага</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">        3. Операции, подходящие по критериям (дата и сумма) будут маркированы зеленой иконкой.</t>
+          <t xml:space="preserve">        2. Операции, подходящие по критериям (дата и сумма) будут маркированы зеленой иконкой.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -544,227 +544,107 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>исправлена нумерация шага «3.» → «2.» (после шага 1 сразу шёл шаг 3, ср. с блоком Authorized ниже); добавлена запятая, закрывающая уточнение «(дата и сумма)»</t>
+          <t>добавлена запятая, закрывающая уточнение «(дата и сумма)»</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        4. Выберите подходящую покупку и нажмите «Компенсировать».</t>
+          <t xml:space="preserve">        1. В приложении «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/) выберите раздел «Уралсиб бонус»  —  далее «Путешествия».</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">        3. Выберите подходящую покупку и нажмите «Компенсировать».</t>
+          <t xml:space="preserve">        1. В приложении «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/) выберите раздел «Уралсиб бонус» — далее «Путешествия».</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>исправлена нумерация шага «4.» → «3.» вслед за исправлением предыдущего шага</t>
+          <t>убраны лишние пробелы вокруг тире</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">        2. Операции, подходящие по критериям (дата и сумма) будут маркированы зеленой иконкой.</t>
+          <t xml:space="preserve">       Бонусные рубли зачисляются на бонусный счет в течение 10 рабочих дней после подтверждения покупки..</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">        2. Операции, подходящие по критериям (дата и сумма), будут маркированы зеленой иконкой.</t>
+          <t xml:space="preserve">       Бонусные рубли зачисляются на бонусный счет в течение 10 рабочих дней после подтверждения покупки.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>добавлена запятая, закрывающая уточнение «(дата и сумма)»</t>
+          <t>убрана лишняя (двойная) точка</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>92</v>
+        <v>154</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">        1. В приложении «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/) выберите раздел «Уралсиб бонус»  —  далее «Путешествия».</t>
+          <t xml:space="preserve">       2. Далее «Управление» –&gt; [«Уралсиб Бонус»]({{$temp.bonusLink}})</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">        1. В приложении «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/) выберите раздел «Уралсиб бонус» — далее «Путешествия».</t>
+          <t xml:space="preserve">       2. Далее «Управление» -&gt; [«Уралсиб Бонус»]({{$temp.bonusLink}})</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>убраны лишние пробелы вокруг тире</t>
+          <t>эн-дефис в стрелке-разделителе заменён на дефис</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">       2. Внизу страницы [«Сервисы»]({{$temp.bonusLink}})</t>
+          <t xml:space="preserve">        • оплата покупки по QR коду или по СБП</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">       2. Внизу страницы [«Сервисы»]({{$temp.bonusLink}}).</t>
+          <t xml:space="preserve">        • оплата покупки по QR-коду или по СБП</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>добавлена точка — для единообразия с первым пунктом списка (стр. 146), где точка есть</t>
+          <t>составное слово «QR-коду» пишется через дефис — для единообразия с остальной базой</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>150</v>
+        <v>242</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">       Бонусные рубли зачисляются на бонусный счет в течение 10 рабочих дней после подтверждения покупки..</t>
+          <t xml:space="preserve">    2. Далее «Управление» - [«Уралсиб Бонус»]({{$temp.bonusLink}})</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">       Бонусные рубли зачисляются на бонусный счет в течение 10 рабочих дней после подтверждения покупки.</t>
+          <t xml:space="preserve">    2. Далее «Управление» -&gt; [«Уралсиб Бонус»]({{$temp.bonusLink}})</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>убрана лишняя (двойная) точка</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>154</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       2. Далее «Управление» –&gt; [«Уралсиб Бонус»]({{$temp.bonusLink}})</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       2. Далее «Управление» -&gt; [«Уралсиб Бонус»]({{$temp.bonusLink}}).</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>эн-дефис в стрелке-разделителе заменён на дефис; добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>169</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        • оплата покупки по QR коду или по СБП</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        • оплата покупки по QR-коду или по СБП</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>составное слово «QR-коду» пишется через дефис — для единообразия с остальной базой</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>201</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Правила бонусной программы указаны на сайте [«Уралсиб Бонус»](https://bonus.uralsib.ru/rules) </t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Правила бонусной программы указаны на сайте [«Уралсиб Бонус»](https://bonus.uralsib.ru/rules). </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>227</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    • В веб-версии на [сайте](https://online.uralsib.ru/). Выберите карту -&gt; внизу страницы «Сервисы»</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    • В веб-версии на [сайте](https://online.uralsib.ru/). Выберите карту -&gt; внизу страницы «Сервисы».</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>добавлена точка — для единообразия с идентичной фразой в файле (стр. 140, 238), где точка есть</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>232</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>balanceLink: Посмотреть баланс бонусного счета вы можете по [ссылке]({{$temp.DBOCardBonusLink}})</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>balanceLink: Посмотреть баланс бонусного счета вы можете по [ссылке]({{$temp.DBOCardBonusLink}}).</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>242</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    2. Далее «Управление» - [«Уралсиб Бонус»]({{$temp.bonusLink}})</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    2. Далее «Управление» -&gt; [«Уралсиб Бонус»]({{$temp.bonusLink}}).</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>одиночный дефис заменён на стрелку «-&gt;» — для единообразия с аналогичными шагами в файле; добавлена точка в конце предложения</t>
+          <t>одиночный дефис заменён на стрелку «-&gt;» — для единообразия с аналогичными шагами в файле</t>
         </is>
       </c>
     </row>
